--- a/samples/library_template_v1.xlsx
+++ b/samples/library_template_v1.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -972,37 +972,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1076,7 +1076,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AE1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.76"/>
@@ -1223,7 +1223,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E44"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="31.71"/>
@@ -1537,7 +1537,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AT38"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.18"/>
@@ -1717,8 +1717,8 @@
       <c r="AR1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AS1" s="0"/>
-      <c r="AT1" s="0"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I2" s="1" t="s">
@@ -4229,7 +4229,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA36"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.18"/>
@@ -5845,7 +5845,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.96"/>
@@ -6625,7 +6625,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
